--- a/final apps/PC/UAT/UAT_PC_TestScript.xlsx
+++ b/final apps/PC/UAT/UAT_PC_TestScript.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +145,9 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G38"/>
+  <dimension ref="B2:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -766,318 +769,365 @@
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>Seeded UAT data (your starting point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>- PC-2026-00008 (SHAIKHA.ALSUWAIDI, TEMPORARY 1,800) - awaiting approval: use for approve/reject tests (approver: AYESHA.AMERI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>- PC-2026-00005 (NASER, TEMPORARY 2,500) - fully approved, awaiting disbursement: use for the Disburse test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>- PC-2026-00006 (AYESHA, TEMPORARY 3,500) - ACTIVE/disbursed: use to create a Clearing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>- PC-2026-00007 (SHAIKHA.GALAMERI, PERMANENT 5,000) - ACTIVE: use to create Reimbursements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>- RMB-2026-00100 (450 on PC-00007) - awaiting approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>Live summary</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Functional area</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Cases</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>Executed %</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Access &amp; Session</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="10">
-        <f>COUNTIF('Access &amp; Session'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E29" s="10">
-        <f>COUNTIF('Access &amp; Session'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F29" s="10">
-        <f>COUNTIF('Access &amp; Session'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G29" s="10">
-        <f>ROUND(COUNTA('Access &amp; Session'!F2:F500)/C29*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="10">
-        <f>COUNTIF('Dashboard'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E30" s="10">
-        <f>COUNTIF('Dashboard'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F30" s="10">
-        <f>COUNTIF('Dashboard'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G30" s="10">
-        <f>ROUND(COUNTA('Dashboard'!F2:F500)/C30*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>My Petty Cash</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" s="10">
-        <f>COUNTIF('My Petty Cash'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E31" s="10">
-        <f>COUNTIF('My Petty Cash'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>COUNTIF('My Petty Cash'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G31" s="10">
-        <f>ROUND(COUNTA('My Petty Cash'!F2:F500)/C31*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Reimbursements</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="10">
-        <f>COUNTIF('Reimbursements'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E32" s="10">
-        <f>COUNTIF('Reimbursements'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F32" s="10">
-        <f>COUNTIF('Reimbursements'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G32" s="10">
-        <f>ROUND(COUNTA('Reimbursements'!F2:F500)/C32*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Clearing</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" s="10">
-        <f>COUNTIF('Clearing'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E33" s="10">
-        <f>COUNTIF('Clearing'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F33" s="10">
-        <f>COUNTIF('Clearing'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G33" s="10">
-        <f>ROUND(COUNTA('Clearing'!F2:F500)/C33*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Approvals</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" s="10">
-        <f>COUNTIF('Approvals'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E34" s="10">
-        <f>COUNTIF('Approvals'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
-        <f>COUNTIF('Approvals'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G34" s="10">
-        <f>ROUND(COUNTA('Approvals'!F2:F500)/C34*100,0)&amp;"%"</f>
-        <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" s="10">
-        <f>COUNTIF('Administration'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E35" s="10">
-        <f>COUNTIF('Administration'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
-        <f>COUNTIF('Administration'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G35" s="10">
-        <f>ROUND(COUNTA('Administration'!F2:F500)/C35*100,0)&amp;"%"</f>
-        <v/>
+          <t>Functional area</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Executed %</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Configuration</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="n">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Access &amp; Session</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D36" s="10">
-        <f>COUNTIF('Configuration'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E36" s="10">
-        <f>COUNTIF('Configuration'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F36" s="10">
-        <f>COUNTIF('Configuration'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G36" s="10">
-        <f>ROUND(COUNTA('Configuration'!F2:F500)/C36*100,0)&amp;"%"</f>
+      <c r="D36" s="11">
+        <f>COUNTIF('Access &amp; Session'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E36" s="11">
+        <f>COUNTIF('Access &amp; Session'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F36" s="11">
+        <f>COUNTIF('Access &amp; Session'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
+        <f>ROUND(COUNTA('Access &amp; Session'!F2:F500)/C36*100,0)&amp;"%"</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Shell &amp; Language</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="n">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D37" s="10">
-        <f>COUNTIF('Shell &amp; Language'!F:F,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E37" s="10">
-        <f>COUNTIF('Shell &amp; Language'!F:F,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F37" s="10">
-        <f>COUNTIF('Shell &amp; Language'!F:F,"Blocked")</f>
-        <v/>
-      </c>
-      <c r="G37" s="10">
-        <f>ROUND(COUNTA('Shell &amp; Language'!F2:F500)/C37*100,0)&amp;"%"</f>
+      <c r="D37" s="11">
+        <f>COUNTIF('Dashboard'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E37" s="11">
+        <f>COUNTIF('Dashboard'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F37" s="11">
+        <f>COUNTIF('Dashboard'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G37" s="11">
+        <f>ROUND(COUNTA('Dashboard'!F2:F500)/C37*100,0)&amp;"%"</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>
+          <t>My Petty Cash</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="11">
+        <f>COUNTIF('My Petty Cash'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E38" s="11">
+        <f>COUNTIF('My Petty Cash'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F38" s="11">
+        <f>COUNTIF('My Petty Cash'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
+        <f>ROUND(COUNTA('My Petty Cash'!F2:F500)/C38*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Reimbursements</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="11">
+        <f>COUNTIF('Reimbursements'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
+        <f>COUNTIF('Reimbursements'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F39" s="11">
+        <f>COUNTIF('Reimbursements'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>ROUND(COUNTA('Reimbursements'!F2:F500)/C39*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Clearing</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="11">
+        <f>COUNTIF('Clearing'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E40" s="11">
+        <f>COUNTIF('Clearing'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F40" s="11">
+        <f>COUNTIF('Clearing'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
+        <f>ROUND(COUNTA('Clearing'!F2:F500)/C40*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="11">
+        <f>COUNTIF('Approvals'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E41" s="11">
+        <f>COUNTIF('Approvals'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F41" s="11">
+        <f>COUNTIF('Approvals'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G41" s="11">
+        <f>ROUND(COUNTA('Approvals'!F2:F500)/C41*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="11">
+        <f>COUNTIF('Administration'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E42" s="11">
+        <f>COUNTIF('Administration'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F42" s="11">
+        <f>COUNTIF('Administration'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>ROUND(COUNTA('Administration'!F2:F500)/C42*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="11">
+        <f>COUNTIF('Configuration'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E43" s="11">
+        <f>COUNTIF('Configuration'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F43" s="11">
+        <f>COUNTIF('Configuration'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>ROUND(COUNTA('Configuration'!F2:F500)/C43*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Shell &amp; Language</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="11">
+        <f>COUNTIF('Shell &amp; Language'!F:F,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E44" s="11">
+        <f>COUNTIF('Shell &amp; Language'!F:F,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F44" s="11">
+        <f>COUNTIF('Shell &amp; Language'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>ROUND(COUNTA('Shell &amp; Language'!F2:F500)/C44*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C38" s="11">
-        <f>SUM(C29:C37)</f>
-        <v/>
-      </c>
-      <c r="D38" s="11">
-        <f>SUM(D29:D37)</f>
-        <v/>
-      </c>
-      <c r="E38" s="11">
-        <f>SUM(E29:E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="11">
-        <f>SUM(F29:F37)</f>
+      <c r="C45" s="12">
+        <f>SUM(C36:C44)</f>
+        <v/>
+      </c>
+      <c r="D45" s="12">
+        <f>SUM(D36:D44)</f>
+        <v/>
+      </c>
+      <c r="E45" s="12">
+        <f>SUM(E36:E44)</f>
+        <v/>
+      </c>
+      <c r="F45" s="12">
+        <f>SUM(F36:F44)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="C7:G7"/>
+  <mergeCells count="22">
     <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C10:G10"/>
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="B17:G17"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="C23:G23"/>
     <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="B30:G30"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1104,146 +1154,146 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-SHL-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Switcher</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Back to Admin / other modules</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Use the top-bar module dropdown</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Other apps open without re-login</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-SHL-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>RTL pass</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Switch to AR
 2. Walk My Petty Cash + Dashboard</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Shell + navigation in Arabic, layout mirrored, amounts keep Latin digits; lists still load</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-SHL-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>PC notifications</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Trigger an approval event
 2. Check the bell</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Notification received and readable</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
@@ -1291,146 +1341,146 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-ACC-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Shared session</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Entry from Admin</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Login in the Admin app
 2. Use the module switcher to open Petty Cash</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>PC opens logged-in (no second login); your name in the top bar</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-ACC-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>No session</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Direct open without login</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Logout (or new private window)
 2. Open the PC app URL directly</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Redirected to the Admin login page</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-ACC-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Role gating</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Approver/Admin menus</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Login as a regular user, then as a PC admin</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Approvals group only for approvers; All Petty Cash/Configuration only for admins</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
@@ -1478,144 +1528,144 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-DSH-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Cards show live numbers</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open PC Dashboard</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Cards (my floats, pending, totals) show sensible non-error values</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-DSH-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Charts</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Floats by org + ageing</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Wait for both charts</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Outstanding floats by organisation bar chart + TEMPORARY ageing chart render correctly</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-DSH-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Charts</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Re-render on return</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Navigate away and back</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Charts render again, not blank/duplicated</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
@@ -1663,100 +1713,100 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-MPC-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>My list</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>My requests only</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open My Petty Cash</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Only YOUR petty cash requests, with number, type, amount, status badge</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-MPC-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>PERMANENT float request</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. New Petty Cash Request
 2. Type=PERMANENT, amount, justification
@@ -1764,204 +1814,204 @@
 4. Save draft</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Draft created with number PC-YYYY-NNNNN; appears in My Petty Cash as DRAFT</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-MPC-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>TEMPORARY float request</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Same with Type=TEMPORARY + needed-by/return date</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Draft created; type shown correctly</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>PC-MPC-04</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Coding must equal amount</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>1. Create a request where coding lines total &lt;&gt; requested amount
 2. Try to submit</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Submission blocked with a clear message</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr"/>
-      <c r="H5" s="15" t="inlineStr"/>
-      <c r="I5" s="14" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>PC-MPC-05</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Required fields</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>1. Try saving with empty amount / justification</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Field-level validation errors; nothing saved</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr"/>
-      <c r="G6" s="15" t="inlineStr"/>
-      <c r="H6" s="15" t="inlineStr"/>
-      <c r="I6" s="14" t="inlineStr"/>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr"/>
+      <c r="H6" s="16" t="inlineStr"/>
+      <c r="I6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>PC-MPC-06</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Submit</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Send for approval</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>1. Open a DRAFT request
 2. Click Submit</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Status changes to submitted/pending; appears in the approver's queue; status history records the event</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr"/>
-      <c r="G7" s="15" t="inlineStr"/>
-      <c r="H7" s="15" t="inlineStr"/>
-      <c r="I7" s="14" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr"/>
+      <c r="H7" s="16" t="inlineStr"/>
+      <c r="I7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>PC-MPC-07</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Request detail</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>1. Open a request from the list</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Full detail: amounts, coding lines, status history timeline, documents</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr"/>
-      <c r="G8" s="15" t="inlineStr"/>
-      <c r="H8" s="15" t="inlineStr"/>
-      <c r="I8" s="14" t="inlineStr"/>
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>PC-MPC-08</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Withdraw</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Withdraw a submitted request</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>1. Open your submitted request
 2. Withdraw</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Status returns to draft/withdrawn; it leaves the approver queue</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr"/>
-      <c r="G9" s="15" t="inlineStr"/>
-      <c r="H9" s="15" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr"/>
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr"/>
+      <c r="H9" s="16" t="inlineStr"/>
+      <c r="I9" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I9"/>
@@ -2009,146 +2059,146 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-RMB-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>New reimbursement</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open Reimbursements &gt; New
 2. Add expense lines (date, GL code, amount, description)
 3. Save + Submit</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Reimbursement created with its own number; goes to approval</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-RMB-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Line items + history</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Open a reimbursement</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Lines, totals, status history all shown</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-RMB-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>My list</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Status tracking</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Check list after submit/approval</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Status badge updates through the lifecycle</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
@@ -2196,147 +2246,147 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-CLR-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Clear a TEMPORARY float</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open Clearing &gt; New for a disbursed TEMPORARY float
 2. Add receipts/expense lines + returned amount
 3. Submit</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Clearing created; float and clearing linked; goes to approval</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-CLR-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Totals must reconcile</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Make receipts + returned cash &lt;&gt; float amount
 2. Try to submit</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Blocked with a clear reconciliation message</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-CLR-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Clearing detail</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Open a clearing record</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Receipt lines, float reference, status history shown</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
@@ -2384,177 +2434,177 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-APR-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Queue</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Pending list (approver)</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Login as approver
 2. Open Approvals</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>All PC items awaiting YOUR step; badge count matches</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-APR-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Approve</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Approve with comment</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Open an item &gt; Approve (+ comment)</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Item leaves queue; requester notified; history shows approver + timestamp + comment</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-APR-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Reject with reason</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Reject another item with a reason</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Status rejected; requester notified with the reason</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>PC-APR-04</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Authorization</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Non-approver blocked</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>1. Login as a regular user
 2. Try the Approvals route</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>No Approvals menu; direct navigation shows no queue/denied</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr"/>
-      <c r="H5" s="15" t="inlineStr"/>
-      <c r="I5" s="14" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I5"/>
@@ -2602,178 +2652,178 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-ADM-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>All Petty Cash</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Paged admin list</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open All Petty Cash (admin)
 2. Check pager '1-50 of N'
 3. Search + filter by status</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>All requests org-wide; server pagination, search and status filter work together</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-ADM-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>All Reimbursements</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Admin list</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Open All Reimbursements</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Org-wide list with status filters</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-ADM-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>All Clearings</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Admin list</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Open All Clearings</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Org-wide list; links open details</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>PC-ADM-04</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Disburse</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Mark approved float disbursed</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>1. Open an APPROVED request
 2. Disburse (date/reference)</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Status becomes DISBURSED; history updated; TEMPORARY floats start ageing</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr"/>
-      <c r="H5" s="15" t="inlineStr"/>
-      <c r="I5" s="14" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I5"/>
@@ -2821,148 +2871,148 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>PC-CFG-01</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>GL codes</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Browse + search combinations</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open GL Codes
 2. Search a segment value</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>9-segment combinations listed with full code string; search filters</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="14" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PC-CFG-02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Approval rules</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>View/edit PC rules</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Open Approval Rules
 2. Review steps/amount thresholds</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Rules display matches the configured approval template</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr"/>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>PC-CFG-03</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Module settings</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>PC settings incl. brand</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Open Module Settings
 2. Edit a setting (e.g. THEME_BRAND_COLOR)
 3. Hard-refresh</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Setting persists; brand color change reflects in PC only (restore afterwards)</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
